--- a/modules/30_q2/figures/editable/origin_templates/data_package/10_拟合RMSE柱状图.xlsx
+++ b/modules/30_q2/figures/editable/origin_templates/data_package/10_拟合RMSE柱状图.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_拟合RMSE柱状图" sheetId="1" r:id="Rff16e5f7da5d41d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_拟合RMSE柱状图" sheetId="1" r:id="R55fb76e29af644b8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,15 +19,15 @@
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:sz val="10"/>
+      <x:sz val="11"/>
       <x:color rgb="FF222222"/>
-      <x:name val="Microsoft YaHei"/>
+      <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="10"/>
+      <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Microsoft YaHei"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
   <x:fills count="3">
@@ -63,24 +63,18 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -283,40 +277,32 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10.75" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="7" t="str">
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="6" t="str">
         <x:v>拟合对象-X</x:v>
       </x:c>
-      <x:c r="B1" s="7" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>RMSE-Y</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="8" t="str">
+      <x:c r="A2" s="2" t="str">
         <x:v>10度单角度</x:v>
       </x:c>
-      <x:c r="B2" s="8" t="n">
-        <x:v>0.0005982024535347983</x:v>
+      <x:c r="B2" s="2" t="n">
+        <x:v>0.0005982024535836858</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="8" t="str">
+      <x:c r="A3" s="2" t="str">
         <x:v>15度单角度</x:v>
       </x:c>
-      <x:c r="B3" s="8" t="n">
-        <x:v>0.0007065215156155058</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="8" t="str">
-        <x:v>双角度联合验证</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="n">
-        <x:v>0.003948535584038329</x:v>
+      <x:c r="B3" s="2" t="n">
+        <x:v>0.000706521515615503</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
